--- a/daily_matches/job_matches_2026-05-21.xlsx
+++ b/daily_matches/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - AI/ML</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, XGBoost, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f0117f05675ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=62e0bd72df7d3118</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Co-Op</t>
+          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rust-Oleum</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vernon Hills, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, Copilot, Hugging Face, TensorFlow, PyTorch, Git, Databricks, Python</t>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3985bb612a4d8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer, Research Biology</t>
+          <t>Forward Deployed Engineer - Applied AI - Senior - Financial Services - Consulting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, AWS SageMaker, Azure ML, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01a962e22a7083c0</t>
+          <t>https://www.indeed.com/viewjob?jk=264d256d1f44f81a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Platform Architect - AI</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Worldpac</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, BigQuery, CI/CD, Terraform, Snowflake, BigQuery, Python, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, FAISS, Pinecone, Prompt Engineering, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e294cc6d33384a45</t>
+          <t>https://www.indeed.com/viewjob?jk=b40bc7a1146e5c89</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>AI Software Engineer (Vehicle Engineering)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Hawthorne, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, Data Lake, MLflow, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116361549f755a48</t>
+          <t>https://www.indeed.com/viewjob?jk=ad497f523694b96c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CG Infinity</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, Git, Snowflake, Redshift, Tableau, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, S3, BigQuery, Docker, CI/CD, Terraform, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior Machine Learning Engineer, Computer Vision</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TTX</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, Git, PySpark, Power BI, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,77 +706,1547 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e77bbafdca99c027</t>
+          <t>https://www.indeed.com/viewjob?jk=808de345c459337e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meazure Learning</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, Synapse, CI/CD, Git, Snowflake, Databricks, BigQuery, Power BI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90eeea46f12e2a00</t>
+          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meazure Learning</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Docker, CI/CD, Terraform, Snowflake, BigQuery</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Full Stack Intern</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Keysight Technologies</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Copilot, S3, EC2, Glue, Docker, Kubernetes, CI/CD, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Architect, Global Insurance</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, CI/CD</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fe34533d5a9fb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Commercial Analytics</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, Azure ML, MLflow, CI/CD, Databricks</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1549117ac932c3e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>High 5 Games</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform, BigQuery</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior AI Developer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc47134ea7a90e7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sr. Data Services Developer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Driscoll's</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Watsonville, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Redshift, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SolarWinds</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, CI/CD, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Wonderist Agency</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Pinecone, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf81fd5e18d4773c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer, Research Biology</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Genentech</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5e7b39b426799a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Walkme</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, MySQL, MongoDB, SQL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37bee16f62d775ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Walkme</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, MySQL, MongoDB, SQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2363b9cbfb0252a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Walkme</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, MySQL, MongoDB, SQL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d9f2d75fa67499b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – MySQL Infrastructure</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, PostgreSQL, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4de9b6cdb31f4141</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Direct Sales Analyst/Developer II</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EchoStar</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, Redshift, Snowflake, Databricks, Redshift, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a6e8aeb332d4a82</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer (Chicago)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fitch Group</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, S3, Docker, Kubernetes, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5dc69845ac12c680</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Capital Group</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b617fed0d5bc808d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LexisNexis Legal &amp; Professional</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>11.1</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11fa14f0ba6a83b9</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c34a95a9e879b898</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac2e1f783d076f1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Software Developer – Cloud Native Platform Engineering</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19d516a61f94ca01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CNPC USA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Copilot, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9a26f03927797f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Software Engineer (USC/GC Only - W2)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ramsoft Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86f156b5713cec77</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Specialist - Software Engineering</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, GitHub Actions, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5606b2a90b826a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Scientist, NA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1128be77fb7a8a6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Core Team</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ZEDEDA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LangChain, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=535367ba427af4a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ancestry</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Terraform, Redshift, Kafka, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d42dabbb94734689</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer, Consumer Product</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Flex</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Snowflake, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53348dfb44ab098b</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr. Professional Services Engineer Consultant</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pendo</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Snowflake, BigQuery, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ef89195818b0e39</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior BI Front End Architect</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Johnson Brothers</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Dataflow, CI/CD, Git, Power BI, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90babb7b0d9adf75</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior BI Front End Architect</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Johnson Brothers</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Dataflow, CI/CD, Git, Power BI, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c5314a6de4eca7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer — AI Operations &amp; Platform Development</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SilverStay</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecbc371e601ffac9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sr. Sales Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Invoca</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=735e3daca51d8077</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sr. Sales Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Invoca</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9145f62250360421</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sr. Sales Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Invoca</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4db200a7952f9f15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sr. Sales Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Invoca</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4b05e5470d700de</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sr. Sales Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Invoca</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4d92f453e54d575</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Customer Engineer, Data &amp; Analytics Req#112</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Premier Cloud</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Git, BigQuery, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=364f355855534524</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>FinTech - AI Finance - Front-end Software Developer - Senior</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, AKS, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37095462c97da019</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Quizlet</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c484b44a04e23c2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Quizlet</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d804d3771702abf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Quizlet</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af2a7567de0386ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Quizlet</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77f654a81eed4cf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, AKS, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6901ef37e35cf939</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-21.xlsx
+++ b/daily_matches/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Ideas2IT Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Docker, Kubernetes</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e0bd72df7d3118</t>
+          <t>https://www.indeed.com/viewjob?jk=65ba785f54845637</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Architect - Data Platform &amp; AI/ML</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>ArsenalTech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks</t>
+          <t>Gemini, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2413d561f12c179</t>
+          <t>https://www.indeed.com/viewjob?jk=fdea458ac4b85502</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - Applied AI - Senior - Financial Services - Consulting</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,104 +556,104 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, AWS SageMaker, Azure ML, Docker</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, S3, Redshift, Docker, Kubernetes, AKS, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=264d256d1f44f81a</t>
+          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Engineering Specialist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Worldpac</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, FAISS, Pinecone, Prompt Engineering, FastAPI, CI/CD</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, S3, Redshift, Docker, Kubernetes, AKS, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b40bc7a1146e5c89</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Software Engineer (Vehicle Engineering)</t>
+          <t>Business Technology Solutions Consultant R&amp;D</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hawthorne, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Data Lake, MLflow, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Redshift, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad497f523694b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=8345f94d3caa21fc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Dot Net Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, S3, BigQuery, Docker, CI/CD, Terraform, Snowflake, BigQuery</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e56c8a333352b48</t>
+          <t>https://www.indeed.com/viewjob?jk=5efceacc40589d5d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Computer Vision</t>
+          <t>Junior Automation Tester (AI enabled Testing)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808de345c459337e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a48d0f78302c9e9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Synapse, CI/CD, Git, Snowflake, Databricks, BigQuery, Power BI</t>
+          <t>RAG, BigQuery, Dataflow, Docker, Jenkins, Git, Databricks, BigQuery, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a037ad0869b5968b</t>
+          <t>https://www.indeed.com/viewjob?jk=198dcb2877451402</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer – Generative AI</t>
+          <t>AWS AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, Docker, CI/CD, Terraform, Snowflake, BigQuery</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd2d5932a298301</t>
+          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
         </is>
       </c>
     </row>
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e62e31febbb7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Architect, Global Insurance</t>
+          <t>Enterprise Architect – Azure AI &amp; Intelligent Platforms</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Inabia Software &amp; Consulting Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, CI/CD</t>
+          <t>Generative AI, RAG, Copilot, MLflow, Docker, Kubernetes, AKS, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,137 +846,137 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fe34533d5a9fb32</t>
+          <t>https://www.indeed.com/viewjob?jk=777126bdf7a69f4f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist, Commercial Analytics</t>
+          <t>Advanced Data Science Associate Consultant - Generative AI and Machine Learning</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, Azure ML, MLflow, CI/CD, Databricks</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1549117ac932c3e4</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc9f1e2057bf76e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer - ML &amp; Data Infrastructure</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>High 5 Games</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform, BigQuery</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b06e51cccf7a7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Developer</t>
+          <t>Senior Java Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc47134ea7a90e7d</t>
+          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Services Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Driscoll's</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Watsonville, CA, US USA</t>
+          <t>Olathe, KS, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Redshift, Tableau, Python, SQL</t>
+          <t>Data Scientist, RAG, Hugging Face, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8cfdb0127f0b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd6de566156014a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SolarWinds</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,252 +1011,252 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, CI/CD, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL</t>
+          <t>Data Scientist, RAG, Glue, Dataflow, CI/CD, Terraform, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c073df0d353c1af</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer II - Organizations</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wonderist Agency</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Pinecone, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf81fd5e18d4773c</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcf26a7d91605c3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer, Research Biology</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Git, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5e7b39b426799a2</t>
+          <t>https://www.indeed.com/viewjob?jk=98639ee5700a8bc5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>Zendesk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, MySQL, MongoDB, SQL</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, Power BI, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bee16f62d775ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2d1a166003bd6f5b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, MySQL, MongoDB, SQL</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Git, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2363b9cbfb0252a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c84e6d717127d82</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, MySQL, MongoDB, SQL</t>
+          <t>RAG, Synapse, CI/CD, GitHub Actions, Git, Databricks, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d9f2d75fa67499b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – MySQL Infrastructure</t>
+          <t>Data Scientist - Graduate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de9b6cdb31f4141</t>
+          <t>https://www.indeed.com/viewjob?jk=b547d783043c40a7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Direct Sales Analyst/Developer II</t>
+          <t>Data Scientist III, Quill</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Staples</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, Redshift, Snowflake, Databricks, Redshift, Tableau, Python, SQL, R, Scala</t>
+          <t>Data Scientist, XGBoost, LightGBM, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6e8aeb332d4a82</t>
+          <t>https://www.indeed.com/viewjob?jk=3b2e57a577b1c5c1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (Chicago)</t>
+          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, S3, Docker, Kubernetes, Python, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc69845ac12c680</t>
+          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>GenAI Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capital Group</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, Terraform, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b617fed0d5bc808d</t>
+          <t>https://www.indeed.com/viewjob?jk=3eebafced953d472</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, Kafka, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c34a95a9e879b898</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, S3, Data Lake, Git, Snowflake, Databricks, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2e1f783d076f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Developer – Cloud Native Platform Engineering</t>
+          <t>Data Engineer-Architecture</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Raiz Federal Credit Union</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d516a61f94ca01</t>
+          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CNPC USA</t>
+          <t>WellBe Senior Medical</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Copilot, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Glue, Dataflow, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a26f03927797f7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Software Engineer (USC/GC Only - W2)</t>
+          <t>Data Science Senior Associate - Digiops Analytics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ramsoft Systems, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Git, Snowflake, Hadoop, Tableau, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f156b5713cec77</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfc58e41b4eb9f3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Specialist - Software Engineering</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, GitHub Actions, Git, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, Redshift, Snowflake, Redshift, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5606b2a90b826a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a57952823f3b727a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Scientist, NA</t>
+          <t>Summer 2026 Intern</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Coupang</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>TensorFlow, PyTorch, XGBoost, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1128be77fb7a8a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec912b15fb976d0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Core Team</t>
+          <t>Summer 2026 Intern</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ZEDEDA</t>
+          <t>Coupang</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LangChain, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>TensorFlow, PyTorch, XGBoost, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=535367ba427af4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=5d85745ef889d532</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer Intern – OPT/CPT Eligible</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ancestry</t>
+          <t>Greenedway</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Terraform, Redshift, Kafka, MySQL, SQL, R, Java</t>
+          <t>Docker, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42dabbb94734689</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f90c9269463462</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Consumer Product</t>
+          <t>Senior Industrial IT/OT Integration Specialist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Snowflake, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, Git, Kafka, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53348dfb44ab098b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5ad5b5db007483</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Professional Services Engineer Consultant</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pendo</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, BigQuery, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Cortex, S3, Glue, Snowflake, Databricks, PySpark, R, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ef89195818b0e39</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior BI Front End Architect</t>
+          <t>MLOps Catastrophe &amp; Geo-Analytics</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Johnson Brothers</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Dataflow, CI/CD, Git, Power BI, SQL, R, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90babb7b0d9adf75</t>
+          <t>https://www.indeed.com/viewjob?jk=50c4a6fcd87a611e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior BI Front End Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Johnson Brothers</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Dataflow, CI/CD, Git, Power BI, SQL, R, Optimization</t>
+          <t>RAG, Synapse, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c5314a6de4eca7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Junior Software Engineer — AI Operations &amp; Platform Development</t>
+          <t>Data Science Analyst - Communications Performance Data (Hybrid)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SilverStay</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,437 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, Git, Power BI, Python, SQL, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbc371e601ffac9</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Sr. Sales Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Invoca</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=735e3daca51d8077</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Sr. Sales Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Invoca</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9145f62250360421</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Sr. Sales Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Invoca</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4db200a7952f9f15</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Sr. Sales Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Invoca</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4b05e5470d700de</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Sr. Sales Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Invoca</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4d92f453e54d575</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Customer Engineer, Data &amp; Analytics Req#112</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Premier Cloud</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Git, BigQuery, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=364f355855534524</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>FinTech - AI Finance - Front-end Software Developer - Senior</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, AKS, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=37095462c97da019</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Quizlet</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, CI/CD, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c484b44a04e23c2d</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Quizlet</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, CI/CD, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d804d3771702abf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Quizlet</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, CI/CD, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af2a7567de0386ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Quizlet</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, CI/CD, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77f654a81eed4cf3</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, AKS, Git, Snowflake, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6901ef37e35cf939</t>
+          <t>https://www.indeed.com/viewjob?jk=f311b8d8b27d7f4c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-21.xlsx
+++ b/daily_matches/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>AI/ML Engineer - Higher Ed</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ideas2IT Technologies</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,129 +496,129 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ba785f54845637</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Software Engineer - Vehicle Cybersecurity</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ArsenalTech</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gemini, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, MLflow, Docker, Kubernetes</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdea458ac4b85502</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb62768f9619d2e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Associate AI/ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, S3, Redshift, Docker, Kubernetes, AKS, Terraform</t>
+          <t>Generative AI, LangChain, RAG, FastAPI, Docker, CI/CD, Terraform, Databricks, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d3da9b71f09aee</t>
+          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineering Specialist</t>
+          <t>AI/ML Engineer - School</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, S3, Redshift, Docker, Kubernetes, AKS, Terraform</t>
+          <t>LangChain, LLaMA, Hugging Face, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd7a3f312b64eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa5fdc8e46d58c2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Business Technology Solutions Consultant R&amp;D</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Redshift, CI/CD, Snowflake, Databricks</t>
+          <t>Data Scientist, RAG, Redshift, Apache Airflow, Git, Snowflake, Redshift, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8345f94d3caa21fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8143f2778929e74b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dot Net Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka</t>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efceacc40589d5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef825bd9f581fc83</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Junior Automation Tester (AI enabled Testing)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
+          <t>Data Scientist, RAG, Copilot, S3, EC2, FastAPI, CI/CD, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a48d0f78302c9e9</t>
+          <t>https://www.indeed.com/viewjob?jk=160fc03f3f3f38b9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Service Delivery Center, Technology, Full Stack Developer, Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Docker, Jenkins, Git, Databricks, BigQuery, Kafka, NoSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198dcb2877451402</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa4542744abd35b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS AI Engineer</t>
+          <t>AI Engineer, Forward Deployed</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>IntegriChain</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Cortex, FastAPI, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,137 +776,137 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8073fabbdb00b63d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c06d99d6a92ae13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Intern</t>
+          <t>AI Analyst - Application Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Waupaca Foundry</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Waupaca, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, S3, EC2, Glue, Docker, Kubernetes, CI/CD, Jenkins, Git, Python</t>
+          <t>LangChain, RAG, Copilot, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c15d01008f879b</t>
+          <t>https://www.indeed.com/viewjob?jk=285b0503724fd91b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Enterprise Architect – Azure AI &amp; Intelligent Platforms</t>
+          <t>Software Engineer - Information Security (Hybrid)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Inabia Software &amp; Consulting Inc.</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, MLflow, Docker, Kubernetes, AKS, CI/CD, Git, Databricks</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777126bdf7a69f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=a25b6019fc20bb16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Advanced Data Science Associate Consultant - Generative AI and Machine Learning</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python</t>
+          <t>Data Scientist, Kinesis, Kubernetes, CI/CD, Terraform, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc9f1e2057bf76e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7973d05d2b02c1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, SQL, R</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Snowflake, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbbafc386f88b28d</t>
+          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer</t>
+          <t>AI Automation Engineer - Sales &amp; Marketing</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, SQL, R</t>
+          <t>LangChain, RAG, Git, Snowflake, Tableau, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27918e064eddd213</t>
+          <t>https://www.indeed.com/viewjob?jk=f70983acbb0fd259</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Olathe, KS, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Hugging Face, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Python, R</t>
+          <t>Data Scientist, RAG, EC2, Docker, Git, Kafka, MongoDB, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd6de566156014a</t>
+          <t>https://www.indeed.com/viewjob?jk=aab0f15b5e95b2ac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Associate - Senior AI Platform Security Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WellBe Senior Medical</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, Dataflow, CI/CD, Terraform, Git, Snowflake, Python, SQL</t>
+          <t>LangChain, RAG, Gemini, BigQuery, Kubernetes, CI/CD, Terraform, BigQuery, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a2a55eff991ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=e60c5181689227fe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II - Organizations</t>
+          <t>Embedded C++ Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, MySQL, Python, SQL, R</t>
+          <t>Cortex, CI/CD, Jenkins, Git, MySQL, Python, SQL, R, C++, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,89 +1056,89 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcf26a7d91605c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a472afc25b8ccbbe</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sunikshainfotech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Git, Kafka, Python, SQL, R, Java</t>
+          <t>Docker, CI/CD, Jenkins, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98639ee5700a8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Data Scientist - Advanced Manufacturing Technologies (AMT)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>US Pharmacopeial Convention</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, Power BI, Python, R, Java</t>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Matplotlib, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d1a166003bd6f5b</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe11419fbd14a46</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Product Maker- Payments and AI Integration</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ninth Wave</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Git, Kafka, Python, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c84e6d717127d82</t>
+          <t>https://www.indeed.com/viewjob?jk=c0d25c08c064872d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, GitHub Actions, Git, Databricks, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d13c7e892b0bc19</t>
+          <t>https://www.indeed.com/viewjob?jk=be8d7c6ccb18a147</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist - Graduate</t>
+          <t>Senior 3D &amp; AI Systems Software Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>CoLab Software</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>RAG, Gemini, Hugging Face, PyTorch, AWS SageMaker, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,602 +1231,42 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b547d783043c40a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c2f0d2780c7b99bd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist III, Quill</t>
+          <t>Associate Data Scientist, New College Grad - 2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Staples</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, LightGBM, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2e57a577b1c5c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer (AI/Cloud Modernization)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30265e60609c6fee</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>GenAI Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>AIG</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Terraform, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3eebafced953d472</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Service Delivery Center, Technology, Back End Developer, Senior</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, Kafka, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6da938c8f9cc21</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Blue Orange Digital</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, S3, Data Lake, Git, Snowflake, Databricks, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0289ffc8e0d406cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Data Engineer-Architecture</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Raiz Federal Credit Union</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>El Paso, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Snowflake, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b2c98f7e4333c03</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>WellBe Senior Medical</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Glue, Dataflow, Git, Snowflake, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f1be584fe969665</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Science Senior Associate - Digiops Analytics</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Git, Snowflake, Hadoop, Tableau, Python, SQL, R, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfc58e41b4eb9f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>National Debt Relief</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, Redshift, Snowflake, Redshift, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a57952823f3b727a</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Summer 2026 Intern</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Coupang</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, XGBoost, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec912b15fb976d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Summer 2026 Intern</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Coupang</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Redmond, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, XGBoost, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d85745ef889d532</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Software Engineer Intern – OPT/CPT Eligible</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Greenedway</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Docker, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f90c9269463462</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Industrial IT/OT Integration Specialist</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ZS Associates</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Data Lake, Git, Kafka, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5ad5b5db007483</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Engineering Specialist</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ZS Associates</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Cortex, S3, Glue, Snowflake, Databricks, PySpark, R, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4509b3b48709b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>MLOps Catastrophe &amp; Geo-Analytics</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Mercury Insurance Company</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, CI/CD, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50c4a6fcd87a611e</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0733e6d33b962b4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Data Science Analyst - Communications Performance Data (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>United Airlines</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, Git, Power BI, Python, SQL, R, Scala, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f311b8d8b27d7f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=f15bdf674e4214d4</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-21.xlsx
+++ b/daily_matches/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Higher Ed</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, Pinecone, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, S3, Glue, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc0ea154c64d7ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6664732c8e57da4b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Vehicle Cybersecurity</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, PyTorch, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb62768f9619d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate AI/ML Engineer</t>
+          <t>Data Engineer V</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Planet DDS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, FastAPI, Docker, CI/CD, Terraform, Databricks, PySpark, Kafka</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64afd722e7be9329</t>
+          <t>https://www.indeed.com/viewjob?jk=b3fecef5d75ec74d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - School</t>
+          <t>Senior AI Full stack Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, LLaMA, Hugging Face, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa5fdc8e46d58c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d159eac40bbe2748</t>
         </is>
       </c>
     </row>
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8143f2778929e74b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc98aa2083c1f9a0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CCS Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef825bd9f581fc83</t>
+          <t>https://www.indeed.com/viewjob?jk=3b498ba8ce91d10a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, S3, EC2, FastAPI, CI/CD, Git, NoSQL, Python</t>
+          <t>RAG, Prompt Engineering, YOLO, Glue, Redshift, CI/CD, Snowflake, Redshift, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=160fc03f3f3f38b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2521221b0a4f471f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Service Delivery Center, Technology, Full Stack Developer, Senior</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Git, Kafka, Python, R</t>
+          <t>RAG, Copilot, Data Lake, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa4542744abd35b</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer, Forward Deployed</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IntegriChain</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Cortex, FastAPI, Git, Snowflake, Python, SQL</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c06d99d6a92ae13</t>
+          <t>https://www.indeed.com/viewjob?jk=b48cfa32c4737ad6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Analyst - Application Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Waupaca Foundry</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Waupaca, WI, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python</t>
+          <t>AI Engineer, RAG, Gemini, Pinecone, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285b0503724fd91b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad962b1ae54c0d4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - Information Security (Hybrid)</t>
+          <t>Omni-Channel Analytics Mgr</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Celebration, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, Prompt Engineering, BigQuery, Docker, Kubernetes, Git, Snowflake, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25b6019fc20bb16</t>
+          <t>https://www.indeed.com/viewjob?jk=09af5471a5399ca3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, X’s Moonshot for Specialized Professional Intelligence</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Kinesis, Kubernetes, CI/CD, Terraform, Kafka, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, FastAPI, CI/CD, Terraform, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7973d05d2b02c1</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc3d8c49bafda48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Advanced Thermal Controls Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Snowflake, BigQuery, Python, SQL, R, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Keras, Git, MySQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389680e185ea40c1</t>
+          <t>https://www.indeed.com/viewjob?jk=3decaddfea59d6c4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Automation Engineer - Sales &amp; Marketing</t>
+          <t>Software engineer, agents</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Writer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Git, Snowflake, Tableau, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70983acbb0fd259</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5558d3193289c8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Software engineer, agents</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Writer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, EC2, Docker, Git, Kafka, MongoDB, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aab0f15b5e95b2ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7ca42296e88c6084</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Associate - Senior AI Platform Security Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>The National Society of Leadership and Success</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Gemini, BigQuery, Kubernetes, CI/CD, Terraform, BigQuery, R, Scala</t>
+          <t>RAG, Copilot, Redshift, Snowflake, Redshift, Tableau, Python, SQL, R, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60c5181689227fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c4021f8f4e89d91f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Embedded C++ Developer</t>
+          <t>Software Engineer, Grad (Recent 2025 Grads)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SmithRx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cortex, CI/CD, Jenkins, Git, MySQL, Python, SQL, R, C++, Scala</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472afc25b8ccbbe</t>
+          <t>https://www.indeed.com/viewjob?jk=a1053262a103bea7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist - Advanced Manufacturing Technologies (AMT)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sunikshainfotech</t>
+          <t>U.S. Pharmacopeia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Jenkins, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Matplotlib, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3b306fbbf582de</t>
+          <t>https://www.indeed.com/viewjob?jk=8c697066e71ec167</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist - Advanced Manufacturing Technologies (AMT)</t>
+          <t>Senior Software Developer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>US Pharmacopeial Convention</t>
+          <t>Global Tax Network</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Maple Grove, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Matplotlib, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Git, NoSQL, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe11419fbd14a46</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2955404226ee4b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Product Maker- Payments and AI Integration</t>
+          <t>Applied AI Senior Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ninth Wave</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Git, Python, R, Java, Scala</t>
+          <t>RAG, TensorFlow, Docker, Kubernetes, Hadoop, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0d25c08c064872d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6d8e33a77e7e27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - AI/ML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be8d7c6ccb18a147</t>
+          <t>https://www.indeed.com/viewjob?jk=39905b752a881a15</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior 3D &amp; AI Systems Software Developer</t>
+          <t>Senior Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CoLab Software</t>
+          <t>Edge Case Research</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Hugging Face, PyTorch, AWS SageMaker, NoSQL, SQL, R, Scala</t>
+          <t>RAG, S3, EC2, CI/CD, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2f0d2780c7b99bd</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fbcec83a5cd1d7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Associate Data Scientist, New College Grad - 2026</t>
+          <t>Analytics Product Owner</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>IHG Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,227 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, Gemini, BigQuery, BigQuery, Tableau, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f15bdf674e4214d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9b65cc5117625ede</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>VEG ER for Pets</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>White Plains, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Copilot, Cortex, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f966211a9a2712e</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Writer</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6316a73541c4b4b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Build Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Realtime Robotics</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae9d4caa8279162c</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DevOps Engineer – Docker &amp; CI/CD</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Optimal Inc.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3e779b560b3f654</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer III</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b634698f1047809</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Cybersecurity &amp; AI Research Intern: AI and Software Development</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LangChain, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Glue, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7ca591c30d54609</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-21.xlsx
+++ b/daily_matches/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Marketing Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Mod Op</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, S3, Glue, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow</t>
+          <t>AI Engineer, LangChain, AWS SageMaker, GCP Vertex AI, Azure ML, Redshift, BigQuery, Synapse, Dataflow, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6664732c8e57da4b</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9d4be577548066</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
+          <t>AWS Dev Ops Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, PyTorch, MLflow, Docker, Kubernetes</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, S3, EC2, Glue, Redshift, MLflow, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79da7babfe0a8608</t>
+          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer V</t>
+          <t>Data Scientist Stf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Planet DDS</t>
+          <t>Leidos QTC Health Services</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, S3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3fecef5d75ec74d</t>
+          <t>https://www.indeed.com/viewjob?jk=39de61bacf1d31b2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Full stack Software Engineer</t>
+          <t>AI/ML Engineer Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d159eac40bbe2748</t>
+          <t>https://www.indeed.com/viewjob?jk=50d98338c0227a30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, Apache Airflow, Git, Snowflake, Redshift, MySQL, MongoDB, NoSQL</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc98aa2083c1f9a0</t>
+          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Sr. Software Engineer, Threat Intelligence</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CCS Inc</t>
+          <t>Proofpoint</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, S3, Docker, Kubernetes, Terraform</t>
+          <t>RAG, EC2, FastAPI, Docker, AKS, CI/CD, GitHub Actions, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,207 +671,207 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b498ba8ce91d10a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6f6e39a72c1b8e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, YOLO, Glue, Redshift, CI/CD, Snowflake, Redshift, Power BI, Python</t>
+          <t>RAG, S3, Kinesis, Snowflake, Kafka, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2521221b0a4f471f</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Salesforce Developer (Hybrid/Columbia MD)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>ForMotiv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Data Lake, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Databricks, Python</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Git, Snowflake, Redshift, Hadoop, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfd9cd9ac48b12f</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9c544471eabb42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integrations Architect- Azure</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, NoSQL, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b48cfa32c4737ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>MCG Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Pinecone, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad962b1ae54c0d4</t>
+          <t>https://www.indeed.com/viewjob?jk=182cec56d83888e9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Omni-Channel Analytics Mgr</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>ForMotiv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Celebration, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, BigQuery, Docker, Kubernetes, Git, Snowflake, BigQuery, Python, SQL</t>
+          <t>RAG, S3, Data Lake, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09af5471a5399ca3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5599acd672ddda</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer, X’s Moonshot for Specialized Professional Intelligence</t>
+          <t>Software Engineer - Backend Services</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Truveta</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, FastAPI, CI/CD, Terraform, NoSQL, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc3d8c49bafda48</t>
+          <t>https://www.indeed.com/viewjob?jk=86db55dacc4ee0a5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Advanced Thermal Controls Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>ForMotiv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Keras, Git, MySQL, Python, SQL, R, Optimization</t>
+          <t>RAG, S3, Redshift, Data Lake, Git, Redshift, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3decaddfea59d6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=13133e87f31e9a8c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software engineer, agents</t>
+          <t>Engineer, TSG Infrastructure</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Writer</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5558d3193289c8</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e0916f7b0c1c3c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software engineer, agents</t>
+          <t>Engineer, TSG Infrastructure</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Writer</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ca42296e88c6084</t>
+          <t>https://www.indeed.com/viewjob?jk=da46be9a61b7b250</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Associate Cloud Platform Engineer - Azure &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The National Society of Leadership and Success</t>
+          <t>InvoiceCloud</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Redshift, Snowflake, Redshift, Tableau, Python, SQL, R, Hypothesis Testing</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,462 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4021f8f4e89d91f</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer, Grad (Recent 2025 Grads)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SmithRx</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1053262a103bea7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Scientist - Advanced Manufacturing Technologies (AMT)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>U.S. Pharmacopeia</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Rockville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Matplotlib, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c697066e71ec167</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Software Developer III</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Global Tax Network</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Maple Grove, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, NoSQL, Power BI, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2955404226ee4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Applied AI Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Sunnyvale, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, Docker, Kubernetes, Hadoop, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6d8e33a77e7e27</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Engineer II - AI/ML</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Blue Origin</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39905b752a881a15</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Full Stack</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Edge Case Research</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, CI/CD, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fbcec83a5cd1d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Analytics Product Owner</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>IHG Hotels &amp; Resorts</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Generative AI, Gemini, BigQuery, BigQuery, Tableau, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b65cc5117625ede</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>VEG ER for Pets</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>White Plains, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Copilot, Cortex, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f966211a9a2712e</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Writer</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6316a73541c4b4b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Build Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Realtime Robotics</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae9d4caa8279162c</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>DevOps Engineer – Docker &amp; CI/CD</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Optimal Inc.</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e779b560b3f654</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer III</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b634698f1047809</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Cybersecurity &amp; AI Research Intern: AI and Software Development</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Siemens</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>LangChain, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Glue, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ca591c30d54609</t>
+          <t>https://www.indeed.com/viewjob?jk=d9bedcae4c767f88</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-21.xlsx
+++ b/daily_matches/job_matches_2026-05-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Marketing Data &amp; AI Engineer</t>
+          <t>Sr. Software Engineer (Go-To-Market AI Team)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mod Op</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, AWS SageMaker, GCP Vertex AI, Azure ML, Redshift, BigQuery, Synapse, Dataflow, Snowflake</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, PyTorch, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9d4be577548066</t>
+          <t>https://www.indeed.com/viewjob?jk=5a92c59262b56cdb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Dev Ops Engineer (Hybrid)</t>
+          <t>Senior Data Engineer (Foundations)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, S3, EC2, Glue, Redshift, MLflow, Docker, CI/CD</t>
+          <t>RAG, Copilot, Cortex, BigQuery, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42661b3f734ffd01</t>
+          <t>https://www.indeed.com/viewjob?jk=0b6fe26cff174d95</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist Stf</t>
+          <t>DevOps Engineer I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Leidos QTC Health Services</t>
+          <t>Altanovo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Vista, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, S3</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39de61bacf1d31b2</t>
+          <t>https://www.indeed.com/viewjob?jk=f31eeb9ca01c77e6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Remote Nationwide or Hybrid in MN/DC</t>
+          <t>Senior DevSecOps Platform Engineer, AI Automation</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>LangChain, RAG, LLaMA, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50d98338c0227a30</t>
+          <t>https://www.indeed.com/viewjob?jk=d56f369e5dbe7882</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>AI Full stack Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, NoSQL</t>
+          <t>LangChain, RAG, LLaMA, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b70ae077b21d43d</t>
+          <t>https://www.indeed.com/viewjob?jk=deb714684be858ef</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Threat Intelligence</t>
+          <t>Sr Associate AI Full stack Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Proofpoint</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,147 +661,147 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, EC2, FastAPI, Docker, AKS, CI/CD, GitHub Actions, Git, PostgreSQL, Python</t>
+          <t>LangChain, RAG, LLaMA, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b6f6e39a72c1b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=7217472d2134a0f8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, Snowflake, Kafka, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6664a8282197f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dbf1260c7d0cc0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ForMotiv</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, Git, Snowflake, Redshift, Hadoop, Python</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9c544471eabb42</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b1713c37555cdd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Integrations Architect- Azure</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, NoSQL, Tableau, Python, SQL</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c88ead1771c841</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d440e3e598ce5c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>SDET- QA Manger</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MCG Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, SQL</t>
+          <t>RAG, Copilot, EC2, Docker, CI/CD, Jenkins, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=182cec56d83888e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6966800cef9464</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer - Contractor</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ForMotiv</t>
+          <t>HealthMark Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,46 +832,46 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>S3, EC2, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5599acd672ddda</t>
+          <t>https://www.indeed.com/viewjob?jk=565fac27a5ad501c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Truveta</t>
+          <t>Boston Energy Trading and Marketing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Python, R, Scala</t>
+          <t>RAG, CI/CD, Snowflake, Databricks, Hadoop, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86db55dacc4ee0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=67ecc5a6b05e7ef0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Software Engineer - Python/Typescript</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ForMotiv</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,126 +902,791 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Data Lake, Git, Redshift, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13133e87f31e9a8c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0f55d628ac408</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Engineer, TSG Infrastructure</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e0916f7b0c1c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d7974c7f716d89</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer, TSG Infrastructure</t>
+          <t>AI/ML Engineer - GTRI-ICL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Matplotlib, Python, SQL, R, Julia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da46be9a61b7b250</t>
+          <t>https://www.indeed.com/viewjob?jk=67ac50fb0338d77b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate Cloud Platform Engineer - Azure &amp; Kubernetes</t>
+          <t>ANALISTA SR DE ML Ops</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>InvoiceCloud</t>
+          <t>Millicom</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Mora, LA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cf7cd0727a04eeb</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Zoom Communications</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfa6d8ef31908627</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Cortex, Apache Airflow, CI/CD, Git, Snowflake, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24134f42e6812501</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Glue, Redshift, Data Lake, CI/CD, Git, Redshift, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ebda74063a09351</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dentsu</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Central, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, MongoDB, NoSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5046bd4e6a29c926</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer- Roleplays</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Yoodli AI Roleplays</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, Kubernetes, Snowflake, Databricks, NoSQL, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2064100512f828d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Guest Travel Insurance (Algorithms)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9bedcae4c767f88</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ada7554505be122a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Zelis Healthcare</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90a531891246468a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JSR Tech Consulting</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Python, SQL, R, Bayesian</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a50e2b274d8c826</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Junior AI Engineer (Open to remote)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, MLflow, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cf7635cad76afd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Development Engineer III, Advertising Technology</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, CI/CD, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe8b16d2305e6089</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Architect, Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Presidio</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3629358a4708fe7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unum</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Cortex, CI/CD, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a6d4cc9c8ea457c</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Associate - Data Scientist</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Oak Ridge National Laboratory</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Oak Ridge, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Python, R, Scala, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8255ea5fefe68d1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92b862d92b1cbb9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer- Platform</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Yoodli AI Roleplays</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kubernetes, Snowflake, Databricks, NoSQL, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61a20d158fe8bf36</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI Transformation Intern</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ensono</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Git, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad268cc8f2b0d246</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Home Loans Loss Forecasting Analytics, Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f7c96e76cf00396</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior R&amp;D Data Scientist</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PDI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Woodcliff Lake, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Python, SQL, R, Scala, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6458687f0324e52</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Experiential Marketing Sr Data Analyst</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a47b94dd54c99961</t>
         </is>
       </c>
     </row>
